--- a/notebooks/data/BigChungus.xlsx
+++ b/notebooks/data/BigChungus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louis\OneDrive\Documenten\UA\Data engineering\KALSHI_PROJECT\Kalshi_economics\notebooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louis\OneDrive\Documenten\UA\Data engineering\KALSHI_PROJECT\Kalshi_economics\notebooks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290ED4D1-BE40-4FCA-9CC8-02E95FBF0E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0152DA0C-0F46-49F7-ACD2-70BC65CC8033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
